--- a/data.mn/public/datasets/mongolbank-money-supply-m1.xlsx
+++ b/data.mn/public/datasets/mongolbank-money-supply-m1.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3625,4 +3626,3224 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B320"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>огноо</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>м1_тэрбум_төгрөг</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>102.559</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2000-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>94.955</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2000-03-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>116.237</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2000-04-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>135.686</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2000-05-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>139.958</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2000-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>143.684</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2000-07-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>138.547</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2000-08-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>140.029</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2000-09-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>143.562</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2000-10-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>133.373</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2000-11-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>120.093</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2000-12-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>130.775</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>116.271</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2001-02-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>120.03</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2001-03-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>123.586</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2001-04-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>138.233</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2001-05-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>150.927</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>155.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2001-07-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>152.485</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2001-08-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>150.335</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2001-09-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>151.809</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2001-10-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>145.792</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2001-11-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>146.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2001-12-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>156.155</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2002-01-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>141.028</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2002-02-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>138.759</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2002-03-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>146.932</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2002-04-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>164.201</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2002-05-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>178.268</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2002-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>187.708</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2002-07-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>185.36</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2002-08-01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>189.423</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2002-09-01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>181.085</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2002-10-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>177.715</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2002-11-01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>175.577</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2002-12-01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>187.728</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>196.578</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2003-02-01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>176.951</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2003-03-01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>180.11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2003-04-01</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>193.596</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2003-05-01</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>200.969</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2003-06-01</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>208.988</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2003-07-01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>204.711</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2003-08-01</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>217.317</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2003-09-01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>214.417</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>213.158</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2003-11-01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>203.785</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2003-12-01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>212.833</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>200.434</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2004-02-01</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>198.111</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2004-03-01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>210.799</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2004-04-01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>225.478</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2004-05-01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>237.218</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2004-06-01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>254.807</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2004-07-01</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>248.765</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>254.029</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>241.995</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>225.739</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>212.579</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>221.328</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>211.272</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2005-02-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>197.123</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2005-03-01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>213.358</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2005-04-01</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>248.013</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2005-05-01</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>255.502</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2005-06-01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>277.664</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2005-07-01</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>278.811</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2005-08-01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>293.241</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2005-09-01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>273.522</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2005-10-01</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>262.138</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2005-11-01</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>253.099</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2005-12-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>269.124</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>267.58</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2006-02-01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>262.114</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2006-03-01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>274.376</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2006-04-01</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>292.829</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2006-05-01</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>326.227</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2006-06-01</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>328.613</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2006-07-01</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>325.023</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2006-08-01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>343.057</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2006-09-01</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>331.263</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2006-10-01</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>320.034</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2006-11-01</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>325.026</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2006-12-01</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>331.903</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>334.997</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2007-02-01</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>342.597</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2007-03-01</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>401.499</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2007-04-01</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>455.119</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2007-05-01</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>490.293</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2007-06-01</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>502.223</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>497.044</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2007-08-01</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>535.468</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2007-09-01</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>515.432</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2007-10-01</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>523.434</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2007-11-01</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>519.932</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2007-12-01</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>590.472</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>551.883</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2008-02-01</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>549.184</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2008-03-01</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>577.707</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2008-04-01</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>583.65</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2008-05-01</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>620.61</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2008-06-01</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>624.894</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2008-07-01</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>624.048</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2008-08-01</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>642.217</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2008-09-01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>603.473</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2008-10-01</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>561.253</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2008-11-01</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>548.309</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2008-12-01</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>647.335</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>535.268</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2009-02-01</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>549.8869999999999</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2009-03-01</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>511.387</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2009-04-01</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>517.898</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2009-05-01</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>559.144</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2009-06-01</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>544.3819999999999</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2009-07-01</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>521.832</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>597.14</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>622.707</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>608.778</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>600.593</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>651.247</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>629.701</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2010-02-01</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>627.897</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2010-03-01</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>693.003</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>754.3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2010-05-01</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>795.658</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2010-06-01</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>839.627</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2010-07-01</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>825.8869999999999</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2010-08-01</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>931.4640000000001</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2010-09-01</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>958.807</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2010-10-01</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1000.376</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2010-11-01</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>995.547</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2010-12-01</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1157.429</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1131.367</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1031.108</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2011-03-01</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1181.381</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2011-04-01</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1338.325</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2011-05-01</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1422.606</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2011-06-01</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1552.472</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2011-07-01</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1559.248</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2011-08-01</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1653.628</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2011-09-01</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1672.567</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2011-10-01</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1619.264</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2011-11-01</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1552.524</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2011-12-01</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1740.944</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2012-01-01</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1565.667</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2012-02-01</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1500.201</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2012-03-01</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1488.042</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2012-04-01</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1595.685</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2012-05-01</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1741.237</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2012-06-01</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1797.055</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2012-07-01</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1660.242</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2012-08-01</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1680.967</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1657.9</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2012-10-01</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1578.621</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2012-11-01</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1557.02</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2012-12-01</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1834.784</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1579.287</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1480.26</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2013-03-01</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1589.075</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1668.191</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2013-05-01</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1779.072</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2026.398</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2013-07-01</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1927.09</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1949.375</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>2013.511</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1936.55</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2013-11-01</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1826.732</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2013-12-01</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>2092.735</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1962.834</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2014-02-01</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1755.05</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2014-03-01</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1737.204</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1845.641</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2014-05-01</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1826.301</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1862.126</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>1698.457</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1874.665</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1836.348</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2014-10-01</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1751.742</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>1689.726</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1816.387</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1578.694</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2015-02-01</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1586.544</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2015-03-01</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1445.928</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1480.863</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2015-05-01</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1689.543</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2015-06-01</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1664.08</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2015-07-01</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>1654.16</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2015-08-01</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1681.847</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2015-09-01</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1613.592</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2015-10-01</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1630.727</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2015-11-01</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1562.732</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2015-12-01</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1685.417</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1608.086</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2016-02-01</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>1522.926</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2016-03-01</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1583.732</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1683.511</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2016-05-01</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1743.872</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2016-06-01</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1982.205</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2016-07-01</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1941.598</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2016-08-01</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1987.871</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>2020.542</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>2087.632</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1928.615</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2016-12-01</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>2147.719</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>2013.274</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2017-02-01</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>2185.648</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>2124.913</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>2313.34</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2017-05-01</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>2487.796</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2017-06-01</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>2719.732</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2017-07-01</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>2584.182</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2759.045</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>2800.401</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2017-10-01</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>2626.536</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2017-11-01</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>2639.511</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>2825.997</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>2632.706</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2018-02-01</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>2733.559</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2018-03-01</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>2776.679</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>2870.981</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2018-05-01</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>3201.396</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>3352.766</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>3090.155</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>3221.728</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>3423.121</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>3444.218</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>3447.022</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2018-12-01</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>4030.954</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>3685.62</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>3465.529</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>3672.886</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>3678.392</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>3806.389</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>4112.154</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>3790.755</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>3943.098</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>3811.936</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>4189.148</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>4003.731</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>3911.413</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>3667.144</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>3489.566</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>3473.531</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>3434.31</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>3637.247</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>3587.984</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>3472.051</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2020-08-01</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>3401.753</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>3571.363</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>3643.212</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>3926.115</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>4212.367</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>3897.905</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>4115.143</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>4342.058</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>5217.959</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>5777.933</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>5979.783</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>5603.343</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>5718.091</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>5620.723</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>5687.668</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>5888.096</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>6507.209</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>5840.556</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>5485.08</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>5723.523</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>5768.183</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>5781.949</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>6067.104</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>5919.787</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>6028.257</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>6174.865</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>6043.764</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>5920.006</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>7201.329</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>6636.65</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>6535.722</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>6792.176</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>7261.715</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>7830.505</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>8281.998</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>8039.058</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>7986.521</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>8189.823</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>8250.973</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>8054.637</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>9853.138999999999</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>8684.647000000001</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>9470.094999999999</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>9789.459000000001</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>9639.698</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>9777.117</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>11807.412</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>12092.814</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>11953.903</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>12067.136</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>10985.492</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>10750.748</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>11687.354</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>10832.175</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>10470.669</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>10137.933</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>9877.294</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>9676.004999999999</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>10645.845</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>10187.59</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>10254.54</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>10504.047</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>10994.292</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>11111.607</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>11227.222</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>11111.606</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>10795.592</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>11057.987</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>12308.633</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>12631.079</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>13582.003</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>12560.034</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.mn/public/datasets/mongolbank-money-supply-m1.xlsx
+++ b/data.mn/public/datasets/mongolbank-money-supply-m1.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3621,6 +3621,26 @@
       </c>
       <c r="B320" t="n">
         <v>12560.034</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>13383.396</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>14521.463</v>
       </c>
     </row>
   </sheetData>
@@ -3634,7 +3654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6843,6 +6863,26 @@
         <v>12560.034</v>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>13383.396</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>14521.463</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
